--- a/data/trans_camb/P0901-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Provincia-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,62; 9,0</t>
+          <t>-2,75; 8,34</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,34; 7,15</t>
+          <t>-3,94; 7,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 3,1</t>
+          <t>-7,5; 3,46</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,55; 15,17</t>
+          <t>-0,54; 15,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,54; 13,59</t>
+          <t>-0,8; 13,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,14; -0,89</t>
+          <t>-12,83; -1,1</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,78; 10,28</t>
+          <t>0,69; 9,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 8,77</t>
+          <t>-0,78; 8,44</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,68; -0,82</t>
+          <t>-8,51; -0,75</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-20,13; 107,05</t>
+          <t>-21,19; 98,71</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,84; 83,13</t>
+          <t>-30,16; 86,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-49,54; 39,18</t>
+          <t>-50,18; 48,46</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1,19; 94,89</t>
+          <t>-1,64; 99,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-7,19; 85,97</t>
+          <t>-3,24; 88,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,89; -4,63</t>
+          <t>-53,11; -5,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,94; 79,29</t>
+          <t>3,67; 72,86</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 67,1</t>
+          <t>-4,48; 63,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-48,55; -6,41</t>
+          <t>-47,0; -4,99</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 5,55</t>
+          <t>-2,12; 5,84</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,4; 2,65</t>
+          <t>-4,57; 2,66</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,68; 12,98</t>
+          <t>3,03; 12,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 5,36</t>
+          <t>-3,8; 6,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 4,16</t>
+          <t>-5,75; 3,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 11,1</t>
+          <t>2,13; 11,27</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 4,56</t>
+          <t>-1,83; 4,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,99</t>
+          <t>-4,18; 2,0</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,47</t>
+          <t>3,79; 10,34</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-21,65; 77,91</t>
+          <t>-20,64; 75,67</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,39; 35,84</t>
+          <t>-39,51; 36,29</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>31,12; 177,01</t>
+          <t>25,7; 165,58</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,18; 34,29</t>
+          <t>-17,98; 40,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,92; 28,54</t>
+          <t>-28,51; 24,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,04; 72,53</t>
+          <t>9,79; 74,51</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 37,68</t>
+          <t>-12,13; 36,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,98; 16,1</t>
+          <t>-27,36; 16,05</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>24,64; 82,03</t>
+          <t>23,69; 84,34</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,48; 10,91</t>
+          <t>1,92; 11,09</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 6,45</t>
+          <t>-1,7; 6,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4,29; 12,87</t>
+          <t>3,68; 13,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 11,76</t>
+          <t>0,04; 11,96</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,25; 3,86</t>
+          <t>-6,59; 3,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,19; 10,4</t>
+          <t>0,23; 10,23</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 9,89</t>
+          <t>2,45; 9,86</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,22; 3,8</t>
+          <t>-2,85; 3,82</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,01; 10,07</t>
+          <t>3,53; 10,17</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,89; 272,53</t>
+          <t>17,44; 255,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,57; 158,43</t>
+          <t>-22,65; 144,37</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>42,32; 293,94</t>
+          <t>34,76; 302,4</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 105,88</t>
+          <t>-1,35; 102,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-43,11; 34,12</t>
+          <t>-42,06; 34,37</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 98,88</t>
+          <t>0,7; 91,88</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>17,78; 116,82</t>
+          <t>19,71; 117,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-27,29; 44,94</t>
+          <t>-24,87; 44,53</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>22,42; 121,6</t>
+          <t>30,78; 123,96</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,03; 15,95</t>
+          <t>6,33; 15,53</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>7,28; 16,93</t>
+          <t>6,95; 16,83</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,5; 20,55</t>
+          <t>9,75; 20,81</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,66; 22,51</t>
+          <t>10,92; 22,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,08; 22,13</t>
+          <t>10,11; 22,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 11,27</t>
+          <t>-5,32; 11,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,53; 17,46</t>
+          <t>9,95; 18,0</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,92; 18,16</t>
+          <t>9,94; 18,05</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 14,31</t>
+          <t>3,13; 13,7</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>81,98; 468,64</t>
+          <t>87,88; 445,48</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>87,92; 488,07</t>
+          <t>91,04; 497,01</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>128,73; 574,96</t>
+          <t>133,21; 649,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>52,98; 162,39</t>
+          <t>56,17; 169,23</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>49,96; 159,93</t>
+          <t>51,09; 167,0</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,09; 79,76</t>
+          <t>-26,3; 83,08</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>74,38; 188,29</t>
+          <t>77,8; 196,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>79,55; 195,7</t>
+          <t>78,18; 189,54</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>31,6; 146,38</t>
+          <t>27,65; 141,68</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 10,74</t>
+          <t>-0,82; 11,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 5,8</t>
+          <t>-4,06; 5,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 4,24</t>
+          <t>-4,97; 4,33</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,66; 20,21</t>
+          <t>5,02; 20,27</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 7,64</t>
+          <t>-4,94; 8,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 5,76</t>
+          <t>-5,14; 6,3</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,27; 14,07</t>
+          <t>4,14; 13,53</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 5,37</t>
+          <t>-3,71; 4,7</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 3,75</t>
+          <t>-3,14; 3,82</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-9,63; 196,03</t>
+          <t>-10,01; 230,36</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-46,36; 115,93</t>
+          <t>-42,41; 115,39</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-49,4; 79,62</t>
+          <t>-46,5; 87,22</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>32,34; 220,31</t>
+          <t>30,75; 226,66</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-36,77; 86,83</t>
+          <t>-33,58; 99,5</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,07; 68,67</t>
+          <t>-31,5; 78,29</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>34,61; 180,75</t>
+          <t>29,96; 174,79</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-25,44; 67,78</t>
+          <t>-31,23; 57,27</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-29,27; 51,26</t>
+          <t>-26,76; 50,61</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 9,0</t>
+          <t>-1,96; 8,96</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,19; 12,8</t>
+          <t>0,74; 12,23</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,03; 7,39</t>
+          <t>-2,26; 7,4</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-6,37; 6,87</t>
+          <t>-5,95; 6,68</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 14,32</t>
+          <t>0,4; 14,07</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-6,11; 5,1</t>
+          <t>-5,61; 4,92</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 6,29</t>
+          <t>-2,17; 6,2</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,71; 11,9</t>
+          <t>2,64; 11,47</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 4,72</t>
+          <t>-2,81; 4,63</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 127,01</t>
+          <t>-15,79; 119,66</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>9,42; 180,71</t>
+          <t>2,79; 154,87</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-17,88; 98,06</t>
+          <t>-19,36; 98,69</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-31,14; 49,49</t>
+          <t>-30,33; 50,68</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 102,0</t>
+          <t>1,07; 99,4</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-29,78; 36,73</t>
+          <t>-27,25; 36,53</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-14,49; 51,99</t>
+          <t>-13,75; 54,92</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>17,41; 104,32</t>
+          <t>18,54; 98,21</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-16,01; 42,06</t>
+          <t>-17,71; 40,93</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 3,21</t>
+          <t>-3,53; 3,18</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 4,94</t>
+          <t>-2,18; 4,97</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,64; 9,06</t>
+          <t>1,61; 9,39</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-2,07; 5,9</t>
+          <t>-1,95; 5,72</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,96; 11,31</t>
+          <t>2,87; 11,13</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 10,75</t>
+          <t>-5,76; 10,94</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 3,44</t>
+          <t>-1,65; 3,57</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,67; 7,06</t>
+          <t>1,52; 7,44</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 8,39</t>
+          <t>-1,64; 8,56</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-30,0; 41,23</t>
+          <t>-31,62; 40,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-17,15; 59,59</t>
+          <t>-19,74; 64,22</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>13,2; 115,92</t>
+          <t>12,99; 118,61</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-13,86; 47,97</t>
+          <t>-12,69; 48,41</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>18,66; 93,01</t>
+          <t>17,7; 90,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-32,91; 80,58</t>
+          <t>-39,47; 82,34</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 32,51</t>
+          <t>-12,32; 34,84</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>13,03; 66,47</t>
+          <t>10,68; 70,71</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-17,67; 74,84</t>
+          <t>-10,12; 77,87</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,57; 4,0</t>
+          <t>-2,78; 3,92</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,96; -1,42</t>
+          <t>-6,83; -1,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,42; 2,19</t>
+          <t>-8,24; 2,29</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 4,91</t>
+          <t>-3,24; 5,24</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 0,27</t>
+          <t>-7,49; 0,47</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 6,52</t>
+          <t>-0,99; 6,42</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,5</t>
+          <t>-1,84; 3,45</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,16; -1,37</t>
+          <t>-6,01; -1,27</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 2,72</t>
+          <t>-6,07; 3,34</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-21,49; 42,27</t>
+          <t>-21,8; 42,11</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-56,46; -14,12</t>
+          <t>-55,6; -11,99</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-65,52; 21,2</t>
+          <t>-62,71; 23,37</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 31,7</t>
+          <t>-16,5; 33,49</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-38,79; 1,19</t>
+          <t>-36,84; 3,29</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 41,49</t>
+          <t>-4,86; 41,21</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 26,65</t>
+          <t>-11,78; 27,53</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-39,44; -10,11</t>
+          <t>-38,68; -9,29</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 19,62</t>
+          <t>-39,76; 24,08</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,52; 4,52</t>
+          <t>1,47; 4,54</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 2,86</t>
+          <t>0,07; 2,92</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1,21; 5,79</t>
+          <t>0,73; 5,68</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,67; 6,41</t>
+          <t>2,56; 6,58</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,05</t>
+          <t>1,35; 4,99</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,78</t>
+          <t>-0,78; 4,92</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,49; 4,92</t>
+          <t>2,54; 5,06</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,06; 3,48</t>
+          <t>1,17; 3,6</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,74</t>
+          <t>1,03; 4,95</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>14,92; 53,7</t>
+          <t>14,95; 54,47</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 33,58</t>
+          <t>0,64; 35,0</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>12,55; 67,29</t>
+          <t>8,15; 66,62</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>15,62; 41,1</t>
+          <t>14,64; 42,34</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>8,47; 32,48</t>
+          <t>7,75; 32,4</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-5,04; 30,37</t>
+          <t>-3,93; 31,54</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,96; 40,72</t>
+          <t>19,02; 41,64</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>7,88; 28,49</t>
+          <t>8,63; 29,42</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>9,7; 39,08</t>
+          <t>8,1; 40,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P0901-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/P0901-Provincia-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,97</t>
+          <t>-2,3</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-7,09</t>
+          <t>-6,46</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-4,5</t>
+          <t>-4,29</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-2,75; 8,34</t>
+          <t>-3,17; 8,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-3,94; 7,15</t>
+          <t>-4,21; 7,25</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 3,46</t>
+          <t>-6,93; 2,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 15,3</t>
+          <t>-0,88; 15,02</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 13,93</t>
+          <t>-1,01; 13,61</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,83; -1,1</t>
+          <t>-12,8; -0,81</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,69; 9,64</t>
+          <t>0,27; 9,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 8,44</t>
+          <t>-1,11; 8,22</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-8,51; -0,75</t>
+          <t>-8,5; -0,66</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-17,83%</t>
+          <t>-20,87%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-35,67%</t>
+          <t>-32,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-29,27%</t>
+          <t>-27,92%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-21,19; 98,71</t>
+          <t>-22,65; 104,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 86,74</t>
+          <t>-30,01; 88,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-50,18; 48,46</t>
+          <t>-50,86; 31,87</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 99,39</t>
+          <t>-2,62; 96,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 88,73</t>
+          <t>-3,76; 87,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-53,11; -5,61</t>
+          <t>-53,3; -4,35</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>3,67; 72,86</t>
+          <t>1,39; 72,82</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 63,36</t>
+          <t>-6,69; 62,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-47,0; -4,99</t>
+          <t>-46,59; -5,26</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>8,06</t>
+          <t>8,62</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>6,56</t>
+          <t>6,05</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7,25</t>
+          <t>7,33</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 5,84</t>
+          <t>-2,42; 5,89</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 2,66</t>
+          <t>-4,58; 2,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,03; 12,72</t>
+          <t>3,72; 13,42</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 6,14</t>
+          <t>-4,44; 5,76</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 3,57</t>
+          <t>-6,13; 3,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,13; 11,27</t>
+          <t>1,47; 10,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,47</t>
+          <t>-1,93; 4,56</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,18; 2,0</t>
+          <t>-4,18; 1,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>3,79; 10,34</t>
+          <t>3,98; 10,75</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>90,67%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>36,39%</t>
+          <t>33,53%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>52,5%</t>
+          <t>53,06%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 75,67</t>
+          <t>-23,31; 77,08</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-39,51; 36,29</t>
+          <t>-40,24; 31,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>25,7; 165,58</t>
+          <t>30,36; 171,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-17,98; 40,83</t>
+          <t>-21,64; 37,67</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 24,72</t>
+          <t>-30,63; 20,91</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,79; 74,51</t>
+          <t>7,2; 71,3</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-12,13; 36,65</t>
+          <t>-12,97; 36,84</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 16,05</t>
+          <t>-27,82; 16,22</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,69; 84,34</t>
+          <t>25,19; 89,09</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8,42</t>
+          <t>8,01</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,24</t>
+          <t>4,79</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>6,84</t>
+          <t>6,43</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,92; 11,09</t>
+          <t>1,2; 10,63</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 6,62</t>
+          <t>-1,26; 7,04</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,68; 13,01</t>
+          <t>3,87; 12,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 11,96</t>
+          <t>-0,09; 11,53</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 3,92</t>
+          <t>-6,88; 3,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,23; 10,23</t>
+          <t>-0,98; 9,28</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,45; 9,86</t>
+          <t>2,23; 10,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,85; 3,82</t>
+          <t>-3,19; 3,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>3,53; 10,17</t>
+          <t>2,69; 9,56</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>137,24%</t>
+          <t>130,58%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>64,11%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,44; 255,15</t>
+          <t>15,21; 250,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,65; 144,37</t>
+          <t>-18,37; 174,96</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>34,76; 302,4</t>
+          <t>43,8; 289,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 102,24</t>
+          <t>-1,02; 106,37</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-42,06; 34,37</t>
+          <t>-41,95; 31,09</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,7; 91,88</t>
+          <t>-5,5; 83,3</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>19,71; 117,82</t>
+          <t>18,51; 122,52</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-24,87; 44,53</t>
+          <t>-29,22; 46,38</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>30,78; 123,96</t>
+          <t>22,43; 116,13</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>14,93</t>
+          <t>13,7</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,06</t>
+          <t>8,88</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9,42</t>
+          <t>11,38</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6,33; 15,53</t>
+          <t>6,46; 15,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>6,95; 16,83</t>
+          <t>7,34; 16,95</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>9,75; 20,81</t>
+          <t>8,77; 19,69</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10,92; 22,87</t>
+          <t>10,54; 22,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,11; 22,41</t>
+          <t>10,0; 22,49</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-5,32; 11,65</t>
+          <t>3,44; 14,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,95; 18,0</t>
+          <t>10,17; 17,82</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,94; 18,05</t>
+          <t>10,04; 18,08</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,13; 13,7</t>
+          <t>7,39; 15,16</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>290,69%</t>
+          <t>266,73%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>25,01%</t>
+          <t>54,62%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>87,34%</t>
+          <t>105,5%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>87,88; 445,48</t>
+          <t>86,13; 469,63</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>91,04; 497,01</t>
+          <t>94,47; 480,56</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>133,21; 649,25</t>
+          <t>114,54; 582,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,17; 169,23</t>
+          <t>54,25; 164,62</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>51,09; 167,0</t>
+          <t>54,41; 164,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-26,3; 83,08</t>
+          <t>18,43; 110,13</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>77,8; 196,26</t>
+          <t>80,33; 188,92</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>78,18; 189,54</t>
+          <t>80,94; 195,32</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>27,65; 141,68</t>
+          <t>56,14; 161,34</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-0,31</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,65</t>
+          <t>0,3</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>-0,13</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 11,21</t>
+          <t>-0,81; 10,7</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 5,9</t>
+          <t>-4,64; 5,53</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,97; 4,33</t>
+          <t>-5,58; 3,38</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5,02; 20,27</t>
+          <t>4,65; 19,82</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-4,94; 8,51</t>
+          <t>-6,19; 7,69</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-5,14; 6,3</t>
+          <t>-5,35; 6,06</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4,14; 13,53</t>
+          <t>4,62; 13,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 4,7</t>
+          <t>-3,29; 5,14</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,82</t>
+          <t>-3,8; 3,3</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-4,06%</t>
+          <t>-10,46%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>-1,32%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 230,36</t>
+          <t>-9,75; 203,75</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-42,41; 115,39</t>
+          <t>-46,81; 109,53</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-46,5; 87,22</t>
+          <t>-52,85; 69,21</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30,75; 226,66</t>
+          <t>23,81; 222,9</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-33,58; 99,5</t>
+          <t>-39,05; 88,47</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-31,5; 78,29</t>
+          <t>-32,8; 75,03</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>29,96; 174,79</t>
+          <t>37,19; 176,19</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-31,23; 57,27</t>
+          <t>-26,75; 66,44</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-26,76; 50,61</t>
+          <t>-30,87; 43,04</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,23</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-0,16</t>
+          <t>-0,3</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>0,89</t>
         </is>
       </c>
     </row>
@@ -1757,47 +1757,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-1,96; 8,96</t>
+          <t>-1,73; 9,41</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,74; 12,23</t>
+          <t>1,52; 12,74</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-2,26; 7,4</t>
+          <t>-2,52; 6,89</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-5,95; 6,68</t>
+          <t>-5,83; 6,75</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>0,4; 14,07</t>
+          <t>0,54; 14,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 4,92</t>
+          <t>-6,04; 4,89</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 6,2</t>
+          <t>-2,25; 6,17</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>2,64; 11,47</t>
+          <t>2,23; 11,61</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 4,63</t>
+          <t>-3,06; 4,55</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-0,91%</t>
+          <t>-1,74%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>6,57%</t>
         </is>
       </c>
     </row>
@@ -1863,47 +1863,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-15,79; 119,66</t>
+          <t>-17,22; 125,61</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2,79; 154,87</t>
+          <t>12,01; 188,1</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 98,69</t>
+          <t>-20,89; 98,79</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-30,33; 50,68</t>
+          <t>-29,53; 47,12</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1,07; 99,4</t>
+          <t>1,34; 100,23</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-27,25; 36,53</t>
+          <t>-28,71; 36,05</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 54,92</t>
+          <t>-15,5; 53,43</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>18,54; 98,21</t>
+          <t>13,79; 99,8</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>-17,71; 40,93</t>
+          <t>-19,15; 39,18</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5,32</t>
+          <t>4,87</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>4,05</t>
+          <t>10,65</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>4,88</t>
+          <t>7,9</t>
         </is>
       </c>
     </row>
@@ -1973,47 +1973,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-3,53; 3,18</t>
+          <t>-3,77; 3,06</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 4,97</t>
+          <t>-2,33; 4,89</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1,61; 9,39</t>
+          <t>1,19; 8,38</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,95; 5,72</t>
+          <t>-2,39; 5,59</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,87; 11,13</t>
+          <t>2,04; 10,77</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 10,94</t>
+          <t>6,78; 14,37</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 3,57</t>
+          <t>-1,92; 3,61</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>1,52; 7,44</t>
+          <t>1,3; 7,16</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 8,56</t>
+          <t>5,21; 10,6</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>55,49%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2051,7 +2051,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>41,32%</t>
+          <t>66,86%</t>
         </is>
       </c>
     </row>
@@ -2079,47 +2079,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-31,62; 40,65</t>
+          <t>-34,05; 39,55</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-19,74; 64,22</t>
+          <t>-20,83; 60,72</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>12,99; 118,61</t>
+          <t>9,01; 106,44</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-12,69; 48,41</t>
+          <t>-15,73; 45,2</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>17,7; 90,54</t>
+          <t>12,9; 89,54</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-39,47; 82,34</t>
+          <t>40,4; 116,89</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 34,84</t>
+          <t>-13,42; 33,96</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
         <is>
-          <t>10,68; 70,71</t>
+          <t>8,71; 67,36</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>-10,12; 77,87</t>
+          <t>39,77; 102,64</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>-2,04</t>
+          <t>0,67</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>1,92</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>-0,54</t>
+          <t>1,28</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 3,92</t>
+          <t>-2,57; 3,91</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>-6,83; -1,14</t>
+          <t>-6,81; -1,15</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-8,24; 2,29</t>
+          <t>-2,47; 3,95</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 5,24</t>
+          <t>-2,93; 4,69</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 0,47</t>
+          <t>-7,37; 0,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 6,42</t>
+          <t>-1,9; 5,61</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 3,45</t>
+          <t>-1,86; 3,12</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>-6,01; -1,27</t>
+          <t>-6,19; -1,49</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>-6,07; 3,34</t>
+          <t>-1,01; 3,72</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>-18,9%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>-3,72%</t>
+          <t>8,86%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>-21,8; 42,11</t>
+          <t>-21,86; 44,76</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>-55,6; -11,99</t>
+          <t>-54,93; -11,14</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-62,71; 23,37</t>
+          <t>-19,73; 42,24</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-16,5; 33,49</t>
+          <t>-15,16; 28,88</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-36,84; 3,29</t>
+          <t>-38,39; 0,1</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 41,21</t>
+          <t>-9,62; 35,74</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>-11,78; 27,53</t>
+          <t>-11,79; 23,5</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>-38,68; -9,29</t>
+          <t>-39,32; -11,24</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>-39,76; 24,08</t>
+          <t>-6,45; 28,89</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2362,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>3,93</t>
+          <t>4,58</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>2,73</t>
+          <t>4,39</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>3,36</t>
+          <t>4,53</t>
         </is>
       </c>
     </row>
@@ -2405,47 +2405,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,54</t>
+          <t>1,37; 4,47</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,07; 2,92</t>
+          <t>-0,08; 2,96</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>0,73; 5,68</t>
+          <t>3,03; 6,17</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2,56; 6,58</t>
+          <t>2,51; 6,55</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,99</t>
+          <t>1,22; 5,02</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 4,92</t>
+          <t>2,65; 6,0</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>2,54; 5,06</t>
+          <t>2,44; 4,94</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
         <is>
-          <t>1,17; 3,6</t>
+          <t>1,16; 3,5</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,95</t>
+          <t>3,41; 5,75</t>
         </is>
       </c>
     </row>
@@ -2468,7 +2468,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>43,45%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>35,52%</t>
         </is>
       </c>
     </row>
@@ -2511,47 +2511,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>14,95; 54,47</t>
+          <t>14,52; 54,36</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0,64; 35,0</t>
+          <t>-0,97; 35,69</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>8,15; 66,62</t>
+          <t>31,09; 73,95</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>14,64; 42,34</t>
+          <t>14,46; 42,39</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>7,75; 32,4</t>
+          <t>6,97; 32,85</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 31,54</t>
+          <t>15,5; 39,32</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>19,02; 41,64</t>
+          <t>18,39; 40,55</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
         <is>
-          <t>8,63; 29,42</t>
+          <t>8,71; 28,63</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>8,1; 40,04</t>
+          <t>25,65; 47,89</t>
         </is>
       </c>
     </row>
